--- a/Simulations_IDS.xlsx
+++ b/Simulations_IDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documentos_Betran\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A6D236-E2B9-4DAA-A6EB-3F6F9534F44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3BB471-06D7-4F6D-AFAB-D622D3F647E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
